--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>3853</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>11.8500003814697</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>11.9499998092651</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>8766</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>12.1000003814697</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>12.1499996185303</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -62917,7 +62917,7 @@
         <v>8766</v>
       </c>
       <c r="C2720" t="n">
-        <v>12.1000003814697</v>
+        <v>12.1499996185303</v>
       </c>
       <c r="D2720" t="n">
         <v>11.8999996185303</v>
@@ -62929,6 +62929,29 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>25615</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>12.4499998092651</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>11.9499998092651</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>12.1499996185303</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>12.4499998092651</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>5492</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>12.4499998092651</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>1998</v>
+        <v>8012</v>
       </c>
       <c r="C2715" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2715" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="E2715" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2715" t="n">
         <v>11.8500003814697</v>
-      </c>
-      <c r="D2715" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="E2715" t="n">
-        <v>11.8500003814697</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>11.8000001907349</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>15832</v>
+        <v>1998</v>
       </c>
       <c r="C2716" t="n">
-        <v>12.1499996185303</v>
+        <v>11.8500003814697</v>
       </c>
       <c r="D2716" t="n">
         <v>11.75</v>
       </c>
       <c r="E2716" t="n">
-        <v>11.75</v>
+        <v>11.8500003814697</v>
       </c>
       <c r="F2716" t="n">
-        <v>12.1000003814697</v>
+        <v>11.8000001907349</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>7072</v>
+        <v>15832</v>
       </c>
       <c r="C2717" t="n">
         <v>12.1499996185303</v>
       </c>
       <c r="D2717" t="n">
-        <v>11.8999996185303</v>
+        <v>11.75</v>
       </c>
       <c r="E2717" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F2717" t="n">
         <v>12.1000003814697</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>12.1499996185303</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>13726</v>
+        <v>7072</v>
       </c>
       <c r="C2718" t="n">
-        <v>12.1999998092651</v>
+        <v>12.1499996185303</v>
       </c>
       <c r="D2718" t="n">
-        <v>11.8500003814697</v>
+        <v>11.8999996185303</v>
       </c>
       <c r="E2718" t="n">
-        <v>11.8500003814697</v>
+        <v>12.1000003814697</v>
       </c>
       <c r="F2718" t="n">
-        <v>11.9499998092651</v>
+        <v>12.1499996185303</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,16 +62888,16 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>3853</v>
+        <v>13726</v>
       </c>
       <c r="C2719" t="n">
-        <v>12</v>
+        <v>12.1999998092651</v>
       </c>
       <c r="D2719" t="n">
-        <v>11.8000001907349</v>
+        <v>11.8500003814697</v>
       </c>
       <c r="E2719" t="n">
         <v>11.8500003814697</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>8766</v>
+        <v>3853</v>
       </c>
       <c r="C2720" t="n">
-        <v>12.1499996185303</v>
+        <v>12</v>
       </c>
       <c r="D2720" t="n">
-        <v>11.8999996185303</v>
+        <v>11.8000001907349</v>
       </c>
       <c r="E2720" t="n">
-        <v>11.8999996185303</v>
+        <v>11.8500003814697</v>
       </c>
       <c r="F2720" t="n">
-        <v>12.1499996185303</v>
+        <v>11.9499998092651</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>25615</v>
+        <v>8766</v>
       </c>
       <c r="C2721" t="n">
-        <v>12.4499998092651</v>
+        <v>12.1499996185303</v>
       </c>
       <c r="D2721" t="n">
-        <v>11.9499998092651</v>
+        <v>11.8999996185303</v>
       </c>
       <c r="E2721" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F2721" t="n">
         <v>12.1499996185303</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>12.4499998092651</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>5492</v>
+        <v>25615</v>
       </c>
       <c r="C2722" t="n">
         <v>12.4499998092651</v>
       </c>
       <c r="D2722" t="n">
+        <v>11.9499998092651</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>12.1499996185303</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>12.4499998092651</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>12130</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D2723" t="n">
         <v>12.25</v>
       </c>
-      <c r="E2722" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="F2722" t="n">
+      <c r="E2723" t="n">
         <v>12.3000001907349</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="F2723" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G2" t="n">
-        <v>1.14870703220367</v>
+        <v>1.14870691299438</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G5" t="n">
-        <v>1.16220510005951</v>
+        <v>1.1622052192688</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G6" t="n">
-        <v>1.18650209903717</v>
+        <v>1.18650221824646</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G9" t="n">
-        <v>1.22632205486298</v>
+        <v>1.22632217407227</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G15" t="n">
-        <v>1.15410614013672</v>
+        <v>1.15410625934601</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G16" t="n">
-        <v>1.20000064373016</v>
+        <v>1.20000040531158</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G19" t="n">
-        <v>1.18650209903717</v>
+        <v>1.18650221824646</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G21" t="n">
-        <v>1.13925814628601</v>
+        <v>1.13925790786743</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G23" t="n">
-        <v>1.13318383693695</v>
+        <v>1.13318395614624</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>1.08323991298676</v>
+        <v>1.08324003219604</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G28" t="n">
-        <v>0.978627979755402</v>
+        <v>0.978627920150757</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G29" t="n">
-        <v>0.987401962280273</v>
+        <v>0.987401843070984</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G30" t="n">
-        <v>0.982677578926086</v>
+        <v>0.982677459716797</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>0.985377252101898</v>
+        <v>0.985377013683319</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>0.985377252101898</v>
+        <v>0.985377013683319</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>1.05624353885651</v>
+        <v>1.05624341964722</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G36" t="n">
-        <v>1.05624353885651</v>
+        <v>1.05624341964722</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G37" t="n">
-        <v>1.0724413394928</v>
+        <v>1.07244157791138</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G42" t="n">
-        <v>1.07986545562744</v>
+        <v>1.07986533641815</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G43" t="n">
-        <v>1.08863937854767</v>
+        <v>1.08863925933838</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G46" t="n">
-        <v>1.07986545562744</v>
+        <v>1.07986533641815</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>1.05624353885651</v>
+        <v>1.05624341964722</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G51" t="n">
-        <v>1.08998918533325</v>
+        <v>1.08998930454254</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G52" t="n">
-        <v>1.06636691093445</v>
+        <v>1.06636703014374</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G53" t="n">
-        <v>1.09066414833069</v>
+        <v>1.09066426753998</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G56" t="n">
-        <v>1.10686218738556</v>
+        <v>1.10686206817627</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G57" t="n">
-        <v>1.13520860671997</v>
+        <v>1.13520848751068</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G60" t="n">
-        <v>1.12778437137604</v>
+        <v>1.12778449058533</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G63" t="n">
-        <v>1.19932556152344</v>
+        <v>1.19932568073273</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G64" t="n">
-        <v>1.1952760219574</v>
+        <v>1.19527626037598</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G65" t="n">
-        <v>1.1952760219574</v>
+        <v>1.19527626037598</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G67" t="n">
-        <v>1.16085529327393</v>
+        <v>1.16085541248322</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.75100004673004</v>
       </c>
       <c r="G70" t="n">
-        <v>1.18177783489227</v>
+        <v>1.18177795410156</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G73" t="n">
-        <v>1.17705345153809</v>
+        <v>1.1770533323288</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G74" t="n">
-        <v>1.19865071773529</v>
+        <v>1.198650598526</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.67299997806549</v>
       </c>
       <c r="G76" t="n">
-        <v>1.12913429737091</v>
+        <v>1.12913417816162</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.70899999141693</v>
       </c>
       <c r="G78" t="n">
-        <v>1.15343129634857</v>
+        <v>1.15343117713928</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G80" t="n">
-        <v>1.15883052349091</v>
+        <v>1.1588306427002</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>1.15883052349091</v>
+        <v>1.1588306427002</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G83" t="n">
-        <v>1.18785178661346</v>
+        <v>1.18785190582275</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>1.18785178661346</v>
+        <v>1.18785190582275</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G85" t="n">
-        <v>1.15545606613159</v>
+        <v>1.1554559469223</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G86" t="n">
-        <v>1.15410614013672</v>
+        <v>1.15410625934601</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>1.15410614013672</v>
+        <v>1.15410625934601</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G88" t="n">
-        <v>1.17975294589996</v>
+        <v>1.17975306510925</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.7389999628067</v>
       </c>
       <c r="G89" t="n">
-        <v>1.17367875576019</v>
+        <v>1.17367887496948</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G91" t="n">
-        <v>1.18785178661346</v>
+        <v>1.18785190582275</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G93" t="n">
-        <v>1.18380236625671</v>
+        <v>1.183802485466</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>1.18785178661346</v>
+        <v>1.18785190582275</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G103" t="n">
-        <v>1.24859428405762</v>
+        <v>1.24859440326691</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G105" t="n">
-        <v>1.22834706306458</v>
+        <v>1.228346824646</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G108" t="n">
-        <v>1.23442113399506</v>
+        <v>1.23442125320435</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G111" t="n">
-        <v>1.19190144538879</v>
+        <v>1.19190168380737</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G114" t="n">
-        <v>1.11226153373718</v>
+        <v>1.11226141452789</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G115" t="n">
-        <v>1.09066414833069</v>
+        <v>1.09066426753998</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>1.08998918533325</v>
+        <v>1.08998930454254</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G117" t="n">
-        <v>1.09943771362305</v>
+        <v>1.09943795204163</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G118" t="n">
-        <v>1.07784056663513</v>
+        <v>1.07784068584442</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>1.07919037342072</v>
+        <v>1.07919061183929</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G120" t="n">
-        <v>1.09471368789673</v>
+        <v>1.09471344947815</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G121" t="n">
-        <v>1.1041624546051</v>
+        <v>1.10416233539581</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G122" t="n">
-        <v>1.10011279582977</v>
+        <v>1.10011303424835</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G123" t="n">
-        <v>1.1041624546051</v>
+        <v>1.10416233539581</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G128" t="n">
-        <v>1.0258721113205</v>
+        <v>1.02587223052979</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G129" t="n">
-        <v>1.03127145767212</v>
+        <v>1.03127157688141</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G130" t="n">
-        <v>1.04274499416351</v>
+        <v>1.04274487495422</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G131" t="n">
-        <v>1.04274499416351</v>
+        <v>1.04274487495422</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G132" t="n">
-        <v>1.04274499416351</v>
+        <v>1.04274487495422</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>1.03937029838562</v>
+        <v>1.03937041759491</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G134" t="n">
-        <v>1.01912307739258</v>
+        <v>1.01912295818329</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G136" t="n">
-        <v>1.06096768379211</v>
+        <v>1.0609678030014</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G137" t="n">
-        <v>1.07784056663513</v>
+        <v>1.07784068584442</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G138" t="n">
-        <v>1.11226153373718</v>
+        <v>1.11226141452789</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G139" t="n">
-        <v>1.10686218738556</v>
+        <v>1.10686206817627</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G140" t="n">
-        <v>1.10686218738556</v>
+        <v>1.10686206817627</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G144" t="n">
-        <v>1.05489349365234</v>
+        <v>1.05489337444305</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G145" t="n">
-        <v>1.05489349365234</v>
+        <v>1.05489337444305</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G146" t="n">
-        <v>1.0724413394928</v>
+        <v>1.07244157791138</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G147" t="n">
-        <v>1.07784056663513</v>
+        <v>1.07784068584442</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G148" t="n">
-        <v>1.07851564884186</v>
+        <v>1.07851576805115</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G149" t="n">
-        <v>1.07851564884186</v>
+        <v>1.07851576805115</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G150" t="n">
-        <v>1.0724413394928</v>
+        <v>1.07244157791138</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.56900000572205</v>
       </c>
       <c r="G151" t="n">
-        <v>1.05894303321838</v>
+        <v>1.05894315242767</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G156" t="n">
-        <v>1.43217146396637</v>
+        <v>1.43217158317566</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G157" t="n">
-        <v>1.43352138996124</v>
+        <v>1.43352127075195</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G158" t="n">
-        <v>1.39842569828033</v>
+        <v>1.39842557907104</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2</v>
       </c>
       <c r="G161" t="n">
-        <v>1.34983193874359</v>
+        <v>1.3498318195343</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G162" t="n">
-        <v>1.41597378253937</v>
+        <v>1.41597354412079</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G163" t="n">
-        <v>1.3849276304245</v>
+        <v>1.38492751121521</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G164" t="n">
-        <v>1.37142908573151</v>
+        <v>1.37142896652222</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G165" t="n">
-        <v>1.38357746601105</v>
+        <v>1.38357758522034</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G167" t="n">
-        <v>1.36467981338501</v>
+        <v>1.36468005180359</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2</v>
       </c>
       <c r="G168" t="n">
-        <v>1.34983193874359</v>
+        <v>1.3498318195343</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G169" t="n">
-        <v>1.37007915973663</v>
+        <v>1.37007927894592</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G170" t="n">
-        <v>1.36602962017059</v>
+        <v>1.36602973937988</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G171" t="n">
-        <v>1.35928058624268</v>
+        <v>1.35928046703339</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G172" t="n">
-        <v>1.37547886371613</v>
+        <v>1.37547862529755</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G173" t="n">
-        <v>1.42677223682404</v>
+        <v>1.42677235603333</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G175" t="n">
-        <v>1.60225045681</v>
+        <v>1.60225033760071</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G176" t="n">
-        <v>1.73453378677368</v>
+        <v>1.73453390598297</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.6340000629425</v>
       </c>
       <c r="G177" t="n">
-        <v>1.77772843837738</v>
+        <v>1.7777281999588</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G179" t="n">
-        <v>1.7250851392746</v>
+        <v>1.72508478164673</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G180" t="n">
-        <v>1.7250851392746</v>
+        <v>1.72508478164673</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G181" t="n">
-        <v>1.70753693580627</v>
+        <v>1.70753729343414</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G183" t="n">
-        <v>1.65354382991791</v>
+        <v>1.65354406833649</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>1.72103536128998</v>
+        <v>1.72103524208069</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>1.77502870559692</v>
+        <v>1.77502858638763</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G187" t="n">
-        <v>1.75883078575134</v>
+        <v>1.75883066654205</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G188" t="n">
-        <v>1.75613105297089</v>
+        <v>1.75613129138947</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G191" t="n">
-        <v>1.77097916603088</v>
+        <v>1.77097940444946</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G192" t="n">
-        <v>1.77637875080109</v>
+        <v>1.7763786315918</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G193" t="n">
-        <v>1.76288032531738</v>
+        <v>1.7628800868988</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G194" t="n">
-        <v>1.76288032531738</v>
+        <v>1.7628800868988</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G195" t="n">
-        <v>1.74803197383881</v>
+        <v>1.74803185462952</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G198" t="n">
-        <v>1.76557993888855</v>
+        <v>1.76557970046997</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G199" t="n">
-        <v>1.78042829036713</v>
+        <v>1.78042805194855</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G200" t="n">
-        <v>1.76557993888855</v>
+        <v>1.76557970046997</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G201" t="n">
-        <v>1.77097916603088</v>
+        <v>1.77097940444946</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G202" t="n">
-        <v>1.80067539215088</v>
+        <v>1.80067551136017</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G203" t="n">
-        <v>1.92216062545776</v>
+        <v>1.92216038703918</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G204" t="n">
-        <v>1.99640095233917</v>
+        <v>1.99640119075775</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G206" t="n">
-        <v>2.01124954223633</v>
+        <v>2.01124930381775</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G207" t="n">
-        <v>1.96535515785217</v>
+        <v>1.96535491943359</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G208" t="n">
-        <v>1.92486000061035</v>
+        <v>1.92485988140106</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G209" t="n">
-        <v>1.95590603351593</v>
+        <v>1.9559063911438</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G210" t="n">
-        <v>1.94510746002197</v>
+        <v>1.94510769844055</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G211" t="n">
-        <v>1.94510746002197</v>
+        <v>1.94510769844055</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G212" t="n">
-        <v>1.92621004581451</v>
+        <v>1.92620992660522</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G214" t="n">
-        <v>2.01664853096008</v>
+        <v>2.01664900779724</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G217" t="n">
-        <v>1.91676115989685</v>
+        <v>1.91676092147827</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G219" t="n">
-        <v>1.89921307563782</v>
+        <v>1.8992133140564</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G220" t="n">
-        <v>1.88166558742523</v>
+        <v>1.88166522979736</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.87800002098083</v>
       </c>
       <c r="G221" t="n">
-        <v>1.94240808486938</v>
+        <v>1.9424079656601</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G222" t="n">
-        <v>1.92890954017639</v>
+        <v>1.92890965938568</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G224" t="n">
-        <v>1.92216062545776</v>
+        <v>1.92216038703918</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G226" t="n">
-        <v>1.86816716194153</v>
+        <v>1.86816728115082</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G227" t="n">
-        <v>1.84926950931549</v>
+        <v>1.84926962852478</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G228" t="n">
-        <v>1.77637875080109</v>
+        <v>1.7763786315918</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G229" t="n">
-        <v>1.75613105297089</v>
+        <v>1.75613129138947</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G230" t="n">
-        <v>1.79527616500854</v>
+        <v>1.79527628421783</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G231" t="n">
-        <v>1.7993255853653</v>
+        <v>1.79932570457458</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G232" t="n">
-        <v>1.81012427806854</v>
+        <v>1.81012451648712</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>1.78852713108063</v>
+        <v>1.78852701187134</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G235" t="n">
-        <v>1.72373521327972</v>
+        <v>1.72373497486115</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G236" t="n">
-        <v>1.72373521327972</v>
+        <v>1.72373497486115</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>1.72103536128998</v>
+        <v>1.72103524208069</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G238" t="n">
-        <v>1.72103536128998</v>
+        <v>1.72103524208069</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G239" t="n">
-        <v>1.73993337154388</v>
+        <v>1.73993313312531</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G240" t="n">
-        <v>1.77097916603088</v>
+        <v>1.77097940444946</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G241" t="n">
-        <v>1.83307123184204</v>
+        <v>1.83307182788849</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G242" t="n">
-        <v>1.84926950931549</v>
+        <v>1.84926962852478</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G243" t="n">
-        <v>1.829021692276</v>
+        <v>1.82902193069458</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G244" t="n">
-        <v>1.83982086181641</v>
+        <v>1.83982074260712</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G245" t="n">
-        <v>1.92351019382477</v>
+        <v>1.92351031303406</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G246" t="n">
-        <v>1.91541135311127</v>
+        <v>1.91541147232056</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G247" t="n">
-        <v>1.91271150112152</v>
+        <v>1.9127117395401</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G248" t="n">
-        <v>1.87086689472198</v>
+        <v>1.87086701393127</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G249" t="n">
-        <v>1.8857147693634</v>
+        <v>1.88571488857269</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G250" t="n">
-        <v>1.8857147693634</v>
+        <v>1.88571488857269</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G251" t="n">
-        <v>1.8897647857666</v>
+        <v>1.88976430892944</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G252" t="n">
-        <v>1.89111435413361</v>
+        <v>1.89111471176147</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G253" t="n">
-        <v>1.89786326885223</v>
+        <v>1.89786350727081</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G254" t="n">
-        <v>1.89921307563782</v>
+        <v>1.8992133140564</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G255" t="n">
-        <v>1.89921307563782</v>
+        <v>1.8992133140564</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G256" t="n">
-        <v>1.89381396770477</v>
+        <v>1.89381372928619</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G259" t="n">
-        <v>1.94510746002197</v>
+        <v>1.94510769844055</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G260" t="n">
-        <v>1.99775123596191</v>
+        <v>1.99775111675262</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G261" t="n">
-        <v>2.10843753814697</v>
+        <v>2.10843729972839</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G262" t="n">
-        <v>2.08548998832703</v>
+        <v>2.08548974990845</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G264" t="n">
-        <v>1.98830246925354</v>
+        <v>1.98830235004425</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>1.99775123596191</v>
+        <v>1.99775111675262</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G266" t="n">
-        <v>1.98830246925354</v>
+        <v>1.98830235004425</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G267" t="n">
-        <v>2.01934838294983</v>
+        <v>2.01934862136841</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G268" t="n">
-        <v>2.03824615478516</v>
+        <v>2.03824591636658</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.01600003242493</v>
       </c>
       <c r="G270" t="n">
-        <v>2.03554630279541</v>
+        <v>2.03554606437683</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>2.05174422264099</v>
+        <v>2.05174446105957</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G274" t="n">
-        <v>2.05579376220703</v>
+        <v>2.05579400062561</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G275" t="n">
-        <v>2.06254291534424</v>
+        <v>2.06254315376282</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G276" t="n">
-        <v>2.07334136962891</v>
+        <v>2.07334184646606</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G278" t="n">
-        <v>2.01124954223633</v>
+        <v>2.01124930381775</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G279" t="n">
-        <v>2.03419637680054</v>
+        <v>2.03419661521912</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G281" t="n">
-        <v>2.01934838294983</v>
+        <v>2.01934862136841</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G282" t="n">
-        <v>2.01934838294983</v>
+        <v>2.01934862136841</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G283" t="n">
-        <v>2.04094529151917</v>
+        <v>2.04094552993774</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.0220000743866</v>
       </c>
       <c r="G285" t="n">
-        <v>2.03959584236145</v>
+        <v>2.03959608078003</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G286" t="n">
-        <v>2.15973091125488</v>
+        <v>2.1597306728363</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G287" t="n">
-        <v>2.39730143547058</v>
+        <v>2.397301197052</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G288" t="n">
-        <v>2.39595150947571</v>
+        <v>2.39595127105713</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.54399991035461</v>
       </c>
       <c r="G290" t="n">
-        <v>2.39190149307251</v>
+        <v>2.39190173149109</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G291" t="n">
-        <v>2.37435412406921</v>
+        <v>2.37435388565063</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G292" t="n">
-        <v>2.31496119499207</v>
+        <v>2.31496143341064</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>2.37570357322693</v>
+        <v>2.37570381164551</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G296" t="n">
-        <v>2.35410690307617</v>
+        <v>2.35410666465759</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G297" t="n">
-        <v>2.35005736351013</v>
+        <v>2.35005712509155</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G302" t="n">
-        <v>2.38245272636414</v>
+        <v>2.38245320320129</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G304" t="n">
-        <v>2.55793142318726</v>
+        <v>2.5579309463501</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G305" t="n">
-        <v>2.61867356300354</v>
+        <v>2.61867380142212</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G307" t="n">
-        <v>2.74285817146301</v>
+        <v>2.74285793304443</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.99662661552429</v>
+        <v>2.99662637710571</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G311" t="n">
-        <v>3.25984358787537</v>
+        <v>3.25984406471252</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>3.44882011413574</v>
+        <v>3.44882035255432</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G315" t="n">
-        <v>3.55680704116821</v>
+        <v>3.55680656433105</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G316" t="n">
-        <v>3.5264356136322</v>
+        <v>3.52643585205078</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G317" t="n">
-        <v>3.56018161773682</v>
+        <v>3.56018137931824</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>3.64454531669617</v>
+        <v>3.6445460319519</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>3.80652594566345</v>
+        <v>3.80652546882629</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>3.91451191902161</v>
+        <v>3.91451168060303</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.9850001335144</v>
       </c>
       <c r="G321" t="n">
-        <v>4.03937196731567</v>
+        <v>4.03937149047852</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>4.01574945449829</v>
+        <v>4.01574993133545</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G323" t="n">
-        <v>3.96175622940063</v>
+        <v>3.96175646781921</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.75500011444092</v>
       </c>
       <c r="G324" t="n">
-        <v>3.88414072990417</v>
+        <v>3.8841404914856</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G325" t="n">
-        <v>4.01574945449829</v>
+        <v>4.01574993133545</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G330" t="n">
-        <v>5.29808902740479</v>
+        <v>5.2980899810791</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G331" t="n">
-        <v>4.61642456054688</v>
+        <v>4.61642503738403</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G332" t="n">
-        <v>4.9133882522583</v>
+        <v>4.91338729858398</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G333" t="n">
-        <v>4.8323974609375</v>
+        <v>4.83239793777466</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G337" t="n">
-        <v>6.1619815826416</v>
+        <v>6.16198205947876</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G338" t="n">
-        <v>6.51293897628784</v>
+        <v>6.51293802261353</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G339" t="n">
-        <v>6.25647115707397</v>
+        <v>6.2564697265625</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>6.46569442749023</v>
+        <v>6.46569299697876</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G341" t="n">
-        <v>6.83298349380493</v>
+        <v>6.83298492431641</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>6.72210454940796</v>
+        <v>6.72210502624512</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.83500003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>6.12265872955322</v>
+        <v>6.12265968322754</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>6.29244422912598</v>
+        <v>6.29244375228882</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>6.11919355392456</v>
+        <v>6.11919450759888</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>6.0914740562439</v>
+        <v>6.09147453308105</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>6.20235347747803</v>
+        <v>6.20235395431519</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G350" t="n">
-        <v>6.27165412902832</v>
+        <v>6.27165365219116</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G353" t="n">
-        <v>5.97019863128662</v>
+        <v>5.97019910812378</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G354" t="n">
-        <v>6.13998460769653</v>
+        <v>6.13998413085938</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.29244422912598</v>
+        <v>6.29244375228882</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G356" t="n">
-        <v>6.23353862762451</v>
+        <v>6.23353815078735</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>6.0949387550354</v>
+        <v>6.09493970870972</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G359" t="n">
-        <v>5.887038230896</v>
+        <v>5.88703918457031</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>5.72071838378906</v>
+        <v>5.72071886062622</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>5.63755893707275</v>
+        <v>5.6375584602356</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G363" t="n">
-        <v>5.68953371047974</v>
+        <v>5.68953323364258</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>8.19499969482422</v>
       </c>
       <c r="G364" t="n">
-        <v>5.67913866043091</v>
+        <v>5.67913913726807</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.99499988555908</v>
       </c>
       <c r="G365" t="n">
-        <v>5.54053831100464</v>
+        <v>5.5405387878418</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>5.48509836196899</v>
+        <v>5.48509883880615</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G367" t="n">
-        <v>5.49202871322632</v>
+        <v>5.49202919006348</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G368" t="n">
-        <v>5.16978406906128</v>
+        <v>5.16978359222412</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.77500009536743</v>
       </c>
       <c r="G369" t="n">
-        <v>4.69507837295532</v>
+        <v>4.69507741928101</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G370" t="n">
-        <v>4.98960256576538</v>
+        <v>4.98960304260254</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>4.78170299530029</v>
+        <v>4.78170347213745</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.7350001335144</v>
       </c>
       <c r="G373" t="n">
-        <v>4.66735792160034</v>
+        <v>4.66735744476318</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G376" t="n">
-        <v>4.52875757217407</v>
+        <v>4.52875852584839</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>4.74358797073364</v>
+        <v>4.74358749389648</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>4.48717784881592</v>
+        <v>4.48717832565308</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.70499992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>4.64656829833984</v>
+        <v>4.646568775177</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.32499980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>4.38322782516479</v>
+        <v>4.38322687149048</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G384" t="n">
-        <v>4.34511280059814</v>
+        <v>4.34511232376099</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G385" t="n">
-        <v>4.32778739929199</v>
+        <v>4.32778787612915</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G386" t="n">
-        <v>4.27581310272217</v>
+        <v>4.27581262588501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G388" t="n">
-        <v>4.22383832931519</v>
+        <v>4.22383737564087</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>4.30006790161133</v>
+        <v>4.30006837844849</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7</v>
       </c>
       <c r="G390" t="n">
-        <v>4.85100364685059</v>
+        <v>4.85100317001343</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.75</v>
       </c>
       <c r="G391" t="n">
-        <v>4.67775344848633</v>
+        <v>4.67775297164917</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G392" t="n">
-        <v>4.63270807266235</v>
+        <v>4.63270854949951</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G394" t="n">
-        <v>4.51143312454224</v>
+        <v>4.51143264770508</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.5</v>
       </c>
       <c r="G395" t="n">
-        <v>4.50450229644775</v>
+        <v>4.50450325012207</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>4.43520307540894</v>
+        <v>4.43520259857178</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>4.42134284973145</v>
+        <v>4.4213433265686</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>4.52875757217407</v>
+        <v>4.52875852584839</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>4.57380199432373</v>
+        <v>4.57380294799805</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G404" t="n">
-        <v>4.58419752120972</v>
+        <v>4.58419799804688</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G406" t="n">
-        <v>4.65349721908569</v>
+        <v>4.65349769592285</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>4.87872362136841</v>
+        <v>4.87872314453125</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>4.95495271682739</v>
+        <v>4.95495367050171</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G409" t="n">
-        <v>4.95495271682739</v>
+        <v>4.95495367050171</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G411" t="n">
-        <v>5.00346374511719</v>
+        <v>5.00346326828003</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G417" t="n">
-        <v>4.72626352310181</v>
+        <v>4.72626304626465</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>4.64310312271118</v>
+        <v>4.64310264587402</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G420" t="n">
-        <v>4.71240377426147</v>
+        <v>4.71240329742432</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G422" t="n">
-        <v>4.86832904815674</v>
+        <v>4.86832809448242</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G423" t="n">
-        <v>4.89258337020874</v>
+        <v>4.8925838470459</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>4.83367824554443</v>
+        <v>4.83367872238159</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G425" t="n">
-        <v>4.72626352310181</v>
+        <v>4.72626304626465</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G428" t="n">
-        <v>4.95495271682739</v>
+        <v>4.95495367050171</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G432" t="n">
-        <v>5.68260383605957</v>
+        <v>5.68260335922241</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G433" t="n">
-        <v>5.56479358673096</v>
+        <v>5.5647931098938</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G434" t="n">
-        <v>5.81427478790283</v>
+        <v>5.81427383422852</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G435" t="n">
-        <v>5.73111391067505</v>
+        <v>5.73111438751221</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G436" t="n">
-        <v>5.72071838378906</v>
+        <v>5.72071886062622</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G438" t="n">
-        <v>5.98059415817261</v>
+        <v>5.98059368133545</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G440" t="n">
-        <v>6.7775444984436</v>
+        <v>6.77754497528076</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>6.642409324646</v>
+        <v>6.64240837097168</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G442" t="n">
-        <v>6.85377407073975</v>
+        <v>6.8537745475769</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G443" t="n">
-        <v>6.87456560134888</v>
+        <v>6.87456464767456</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G444" t="n">
-        <v>7.41510534286499</v>
+        <v>7.41510486602783</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G447" t="n">
-        <v>8.62785625457764</v>
+        <v>8.62785530090332</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G450" t="n">
-        <v>8.11503601074219</v>
+        <v>8.11503505706787</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G454" t="n">
-        <v>7.72002553939819</v>
+        <v>7.72002506256104</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>7.5190544128418</v>
+        <v>7.51905536651611</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G457" t="n">
-        <v>7.69923543930054</v>
+        <v>7.69923400878906</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>7.69230604171753</v>
+        <v>7.69230556488037</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G460" t="n">
-        <v>7.5952844619751</v>
+        <v>7.59528541564941</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G462" t="n">
-        <v>7.41510534286499</v>
+        <v>7.41510486602783</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G464" t="n">
-        <v>7.2695746421814</v>
+        <v>7.26957559585571</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G466" t="n">
-        <v>7.17948389053345</v>
+        <v>7.17948436737061</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G468" t="n">
-        <v>7.11711454391479</v>
+        <v>7.11711502075195</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>7.93485546112061</v>
+        <v>7.93485450744629</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G470" t="n">
-        <v>7.55370473861694</v>
+        <v>7.5537052154541</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G471" t="n">
-        <v>7.66458511352539</v>
+        <v>7.66458654403687</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G472" t="n">
-        <v>7.56063461303711</v>
+        <v>7.56063652038574</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G473" t="n">
-        <v>7.74774503707886</v>
+        <v>7.74774599075317</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G474" t="n">
-        <v>7.63686466217041</v>
+        <v>7.63686561584473</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G475" t="n">
-        <v>7.56756401062012</v>
+        <v>7.56756544113159</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G476" t="n">
-        <v>7.46361494064331</v>
+        <v>7.46361589431763</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G478" t="n">
-        <v>7.15176439285278</v>
+        <v>7.15176486968994</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G481" t="n">
-        <v>6.70824480056763</v>
+        <v>6.70824432373047</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G485" t="n">
-        <v>6.93693399429321</v>
+        <v>6.93693447113037</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G489" t="n">
-        <v>7.37352418899536</v>
+        <v>7.37352514266968</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G491" t="n">
-        <v>6.98544454574585</v>
+        <v>6.98544502258301</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G492" t="n">
-        <v>6.97851467132568</v>
+        <v>6.97851514816284</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G494" t="n">
-        <v>6.92307424545288</v>
+        <v>6.92307376861572</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>9.875</v>
       </c>
       <c r="G495" t="n">
-        <v>6.84337949752808</v>
+        <v>6.84337997436523</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G496" t="n">
-        <v>6.74982452392578</v>
+        <v>6.74982357025146</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>6.6458740234375</v>
+        <v>6.64587354660034</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>6.6978497505188</v>
+        <v>6.69784832000732</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>6.89535474777222</v>
+        <v>6.89535522460938</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G501" t="n">
-        <v>6.60429382324219</v>
+        <v>6.60429430007935</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G502" t="n">
-        <v>6.63894510269165</v>
+        <v>6.63894414901733</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G503" t="n">
-        <v>6.53845977783203</v>
+        <v>6.53845882415771</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G504" t="n">
-        <v>6.70131397247314</v>
+        <v>6.7013144493103</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G505" t="n">
-        <v>6.70824480056763</v>
+        <v>6.70824432373047</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>6.642409324646</v>
+        <v>6.64240837097168</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G507" t="n">
-        <v>6.70824480056763</v>
+        <v>6.70824432373047</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G508" t="n">
-        <v>6.68052434921265</v>
+        <v>6.68052387237549</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.70499992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>6.72556972503662</v>
+        <v>6.72556924819946</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.95499992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>6.89881992340088</v>
+        <v>6.89882040023804</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G511" t="n">
-        <v>6.87802982330322</v>
+        <v>6.87802934646606</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G513" t="n">
-        <v>7.068603515625</v>
+        <v>7.06860399246216</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G514" t="n">
-        <v>7.56756401062012</v>
+        <v>7.56756544113159</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G515" t="n">
-        <v>7.53984451293945</v>
+        <v>7.53984594345093</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G516" t="n">
-        <v>7.95564460754395</v>
+        <v>7.9556450843811</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G517" t="n">
-        <v>7.85862398147583</v>
+        <v>7.85862493515015</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>7.69230604171753</v>
+        <v>7.69230556488037</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11</v>
       </c>
       <c r="G519" t="n">
-        <v>7.62300395965576</v>
+        <v>7.62300491333008</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>11</v>
       </c>
       <c r="G520" t="n">
-        <v>7.62300395965576</v>
+        <v>7.62300491333008</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G521" t="n">
-        <v>7.6091456413269</v>
+        <v>7.60914468765259</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>11</v>
       </c>
       <c r="G522" t="n">
-        <v>7.62300395965576</v>
+        <v>7.62300491333008</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11</v>
       </c>
       <c r="G523" t="n">
-        <v>7.62300395965576</v>
+        <v>7.62300491333008</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>7.69230604171753</v>
+        <v>7.69230556488037</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11</v>
       </c>
       <c r="G525" t="n">
-        <v>7.62300395965576</v>
+        <v>7.62300491333008</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G526" t="n">
-        <v>7.53984451293945</v>
+        <v>7.53984594345093</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G527" t="n">
-        <v>7.6091456413269</v>
+        <v>7.60914468765259</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G529" t="n">
-        <v>7.38738346099854</v>
+        <v>7.38738393783569</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>7.48440504074097</v>
+        <v>7.48440551757812</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>11</v>
       </c>
       <c r="G531" t="n">
-        <v>7.62300395965576</v>
+        <v>7.62300491333008</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G532" t="n">
-        <v>7.41510534286499</v>
+        <v>7.41510486602783</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G533" t="n">
-        <v>7.35966491699219</v>
+        <v>7.35966396331787</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G536" t="n">
-        <v>6.85377407073975</v>
+        <v>6.8537745475769</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G537" t="n">
-        <v>6.54192447662354</v>
+        <v>6.54192399978638</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>6.87456560134888</v>
+        <v>6.87456464767456</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>6.50034475326538</v>
+        <v>6.50034427642822</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G541" t="n">
-        <v>6.39639472961426</v>
+        <v>6.3963942527771</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G542" t="n">
-        <v>6.25086498260498</v>
+        <v>6.25086545944214</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G544" t="n">
-        <v>6.39639472961426</v>
+        <v>6.3963942527771</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G545" t="n">
-        <v>6.6458740234375</v>
+        <v>6.64587354660034</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>6.38253498077393</v>
+        <v>6.38253402709961</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G547" t="n">
-        <v>6.3201642036438</v>
+        <v>6.32016372680664</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G549" t="n">
-        <v>6.25086498260498</v>
+        <v>6.25086545944214</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G551" t="n">
-        <v>6.31323385238647</v>
+        <v>6.31323432922363</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G552" t="n">
-        <v>6.05682420730591</v>
+        <v>6.05682468414307</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G553" t="n">
-        <v>5.96673345565796</v>
+        <v>5.96673393249512</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G555" t="n">
-        <v>5.66181373596191</v>
+        <v>5.66181421279907</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G558" t="n">
-        <v>6.02910327911377</v>
+        <v>6.02910423278809</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G562" t="n">
-        <v>6.4310450553894</v>
+        <v>6.43104410171509</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G563" t="n">
-        <v>6.25086498260498</v>
+        <v>6.25086545944214</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G564" t="n">
-        <v>6.2785849571228</v>
+        <v>6.27858448028564</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G565" t="n">
-        <v>6.2785849571228</v>
+        <v>6.27858448028564</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>6.27165412902832</v>
+        <v>6.27165365219116</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>8.75</v>
       </c>
       <c r="G569" t="n">
-        <v>6.06375360488892</v>
+        <v>6.06375455856323</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G570" t="n">
-        <v>5.96673345565796</v>
+        <v>5.96673393249512</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G573" t="n">
-        <v>5.71032333374023</v>
+        <v>5.71032428741455</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G575" t="n">
-        <v>5.67567348480225</v>
+        <v>5.67567300796509</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G578" t="n">
-        <v>5.68953371047974</v>
+        <v>5.68953323364258</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G579" t="n">
-        <v>5.71032333374023</v>
+        <v>5.71032428741455</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G580" t="n">
-        <v>5.79348278045654</v>
+        <v>5.7934832572937</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>5.77269411087036</v>
+        <v>5.7726936340332</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>5.94594383239746</v>
+        <v>5.94594430923462</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G583" t="n">
-        <v>5.95980405807495</v>
+        <v>5.95980453491211</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G584" t="n">
-        <v>6.02217388153076</v>
+        <v>6.02217435836792</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>5.99445343017578</v>
+        <v>5.99445390701294</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>5.95980405807495</v>
+        <v>5.95980453491211</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G588" t="n">
-        <v>5.89743423461914</v>
+        <v>5.89743375778198</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G593" t="n">
-        <v>6.0706844329834</v>
+        <v>6.07068490982056</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G594" t="n">
-        <v>5.99445343017578</v>
+        <v>5.99445390701294</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G596" t="n">
-        <v>5.99445343017578</v>
+        <v>5.99445390701294</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G599" t="n">
-        <v>6.14863443374634</v>
+        <v>6.1486349105835</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G600" t="n">
-        <v>6.22801876068115</v>
+        <v>6.22801780700684</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G601" t="n">
-        <v>6.11976671218872</v>
+        <v>6.11976718902588</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G604" t="n">
-        <v>6.17750072479248</v>
+        <v>6.17750120162964</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.73728227615356</v>
+        <v>5.73728179931641</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G609" t="n">
-        <v>5.72284841537476</v>
+        <v>5.72284889221191</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>5.65068101882935</v>
+        <v>5.65068197250366</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G612" t="n">
-        <v>5.62903213500977</v>
+        <v>5.62903118133545</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G614" t="n">
-        <v>5.28262996673584</v>
+        <v>5.28262948989868</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>5.35479688644409</v>
+        <v>5.35479593276978</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>7.75</v>
       </c>
       <c r="G618" t="n">
-        <v>5.5929479598999</v>
+        <v>5.59294843673706</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>5.57851457595825</v>
+        <v>5.57851409912109</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G622" t="n">
-        <v>5.54964780807495</v>
+        <v>5.54964733123779</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G626" t="n">
-        <v>6.09811687469482</v>
+        <v>6.09811735153198</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>8.75</v>
       </c>
       <c r="G627" t="n">
-        <v>6.31461906433105</v>
+        <v>6.3146185874939</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G629" t="n">
-        <v>6.10533332824707</v>
+        <v>6.10533380508423</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G632" t="n">
-        <v>5.83831644058228</v>
+        <v>5.83831596374512</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G633" t="n">
-        <v>5.5640811920166</v>
+        <v>5.56408071517944</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.55686473846436</v>
+        <v>5.5568642616272</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G635" t="n">
-        <v>5.49191427230835</v>
+        <v>5.49191379547119</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G636" t="n">
-        <v>5.35479688644409</v>
+        <v>5.35479593276978</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G639" t="n">
-        <v>5.49191427230835</v>
+        <v>5.49191379547119</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G645" t="n">
-        <v>5.4197473526001</v>
+        <v>5.41974687576294</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G650" t="n">
-        <v>5.37644577026367</v>
+        <v>5.37644672393799</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>5.12386131286621</v>
+        <v>5.12386178970337</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G656" t="n">
-        <v>5.08777856826782</v>
+        <v>5.08777809143066</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G657" t="n">
-        <v>5.22489547729492</v>
+        <v>5.22489500045776</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>5.35479688644409</v>
+        <v>5.35479593276978</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G661" t="n">
-        <v>5.16716194152832</v>
+        <v>5.16716241836548</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>5.08056116104126</v>
+        <v>5.08056163787842</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G663" t="n">
-        <v>4.99396133422852</v>
+        <v>4.99396085739136</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G664" t="n">
-        <v>5.01561069488525</v>
+        <v>5.01561117172241</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G666" t="n">
-        <v>5.55686473846436</v>
+        <v>5.5568642616272</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G667" t="n">
-        <v>5.53521394729614</v>
+        <v>5.5352144241333</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G669" t="n">
-        <v>5.22489547729492</v>
+        <v>5.22489500045776</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>5.12386131286621</v>
+        <v>5.12386178970337</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>5.02282762527466</v>
+        <v>5.0228271484375</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G672" t="n">
-        <v>4.99396133422852</v>
+        <v>4.99396085739136</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G673" t="n">
-        <v>4.99396133422852</v>
+        <v>4.99396085739136</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>4.8857102394104</v>
+        <v>4.88570976257324</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>6.5</v>
       </c>
       <c r="G683" t="n">
-        <v>4.69085931777954</v>
+        <v>4.6908597946167</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G685" t="n">
-        <v>4.59704160690308</v>
+        <v>4.59704256057739</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>4.70529270172119</v>
+        <v>4.70529365539551</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G688" t="n">
-        <v>4.58260917663574</v>
+        <v>4.58260869979858</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>4.68364286422729</v>
+        <v>4.68364238739014</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>4.73415994644165</v>
+        <v>4.73415946960449</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G691" t="n">
-        <v>4.68364286422729</v>
+        <v>4.68364238739014</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G693" t="n">
-        <v>4.67642545700073</v>
+        <v>4.67642593383789</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G694" t="n">
-        <v>4.7702431678772</v>
+        <v>4.77024364471436</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>4.90014362335205</v>
+        <v>4.90014410018921</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.943443775177</v>
+        <v>4.94344329833984</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G699" t="n">
-        <v>5.98986673355103</v>
+        <v>5.98986721038818</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G700" t="n">
-        <v>5.83831644058228</v>
+        <v>5.83831596374512</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G702" t="n">
-        <v>5.79501485824585</v>
+        <v>5.79501533508301</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G705" t="n">
-        <v>5.72284841537476</v>
+        <v>5.72284889221191</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G706" t="n">
-        <v>5.22489547729492</v>
+        <v>5.22489500045776</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G707" t="n">
-        <v>4.943443775177</v>
+        <v>4.94344329833984</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G709" t="n">
-        <v>4.85684394836426</v>
+        <v>4.8568434715271</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>4.7991099357605</v>
+        <v>4.79911041259766</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G711" t="n">
-        <v>4.76302623748779</v>
+        <v>4.76302671432495</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>4.71250915527344</v>
+        <v>4.7125096321106</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G718" t="n">
-        <v>4.76302623748779</v>
+        <v>4.76302671432495</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G719" t="n">
-        <v>4.71250915527344</v>
+        <v>4.7125096321106</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G720" t="n">
-        <v>4.77745914459229</v>
+        <v>4.7774600982666</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G721" t="n">
-        <v>4.59704160690308</v>
+        <v>4.59704256057739</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G722" t="n">
-        <v>4.64034175872803</v>
+        <v>4.64034223556519</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G723" t="n">
-        <v>4.61869287490845</v>
+        <v>4.61869239807129</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G724" t="n">
-        <v>4.61147546768188</v>
+        <v>4.61147594451904</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>4.65477561950684</v>
+        <v>4.65477609634399</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G726" t="n">
-        <v>4.77745914459229</v>
+        <v>4.7774600982666</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>4.73415994644165</v>
+        <v>4.73415946960449</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>4.70529270172119</v>
+        <v>4.70529365539551</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G729" t="n">
-        <v>4.79189300537109</v>
+        <v>4.79189252853394</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G730" t="n">
-        <v>4.73415994644165</v>
+        <v>4.73415946960449</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G735" t="n">
-        <v>4.11352252960205</v>
+        <v>4.11352300643921</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G736" t="n">
-        <v>4.22177314758301</v>
+        <v>4.22177410125732</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G739" t="n">
-        <v>4.0124888420105</v>
+        <v>4.01248931884766</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G741" t="n">
-        <v>4.15682411193848</v>
+        <v>4.15682363510132</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>4.30115795135498</v>
+        <v>4.30115699768066</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G746" t="n">
-        <v>4.8857102394104</v>
+        <v>4.88570976257324</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>5.08777856826782</v>
+        <v>5.08777809143066</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G749" t="n">
-        <v>4.89292812347412</v>
+        <v>4.89292764663696</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G751" t="n">
-        <v>4.82797718048096</v>
+        <v>4.8279767036438</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G755" t="n">
-        <v>5.0300440788269</v>
+        <v>5.03004503250122</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>5.06612777709961</v>
+        <v>5.06612825393677</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G759" t="n">
-        <v>5.09499406814575</v>
+        <v>5.09499549865723</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G760" t="n">
-        <v>4.97231101989746</v>
+        <v>4.97231149673462</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G761" t="n">
-        <v>4.79189300537109</v>
+        <v>4.79189252853394</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G762" t="n">
-        <v>4.65477561950684</v>
+        <v>4.65477609634399</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G764" t="n">
-        <v>5.01561069488525</v>
+        <v>5.01561117172241</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>5.08056116104126</v>
+        <v>5.08056163787842</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G767" t="n">
-        <v>5.11664485931396</v>
+        <v>5.11664533615112</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G768" t="n">
-        <v>5.02282762527466</v>
+        <v>5.0228271484375</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>5.17437934875488</v>
+        <v>5.17437887191772</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G771" t="n">
-        <v>5.24654626846313</v>
+        <v>5.24654579162598</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G774" t="n">
-        <v>5.25376272201538</v>
+        <v>5.25376224517822</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G775" t="n">
-        <v>5.21046257019043</v>
+        <v>5.21046209335327</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G777" t="n">
-        <v>5.6795482635498</v>
+        <v>5.67954730987549</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G778" t="n">
-        <v>5.64346504211426</v>
+        <v>5.6434645652771</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>5.89604997634888</v>
+        <v>5.89604949951172</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>7.75</v>
       </c>
       <c r="G782" t="n">
-        <v>5.5929479598999</v>
+        <v>5.59294843673706</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G783" t="n">
-        <v>5.72284841537476</v>
+        <v>5.72284889221191</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>7.75</v>
       </c>
       <c r="G785" t="n">
-        <v>5.5929479598999</v>
+        <v>5.59294843673706</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>5.55686473846436</v>
+        <v>5.5568642616272</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G789" t="n">
-        <v>5.78058195114136</v>
+        <v>5.78058242797852</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G791" t="n">
-        <v>5.58573055267334</v>
+        <v>5.5857310295105</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G796" t="n">
-        <v>5.80944967269897</v>
+        <v>5.80944871902466</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G797" t="n">
-        <v>5.78779935836792</v>
+        <v>5.78779983520508</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G798" t="n">
-        <v>5.73728227615356</v>
+        <v>5.73728179931641</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G802" t="n">
-        <v>5.64346504211426</v>
+        <v>5.6434645652771</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G804" t="n">
-        <v>5.62903213500977</v>
+        <v>5.62903118133545</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>5.62181377410889</v>
+        <v>5.6218147277832</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G806" t="n">
-        <v>5.64346504211426</v>
+        <v>5.6434645652771</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G817" t="n">
-        <v>5.81666612625122</v>
+        <v>5.81666660308838</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>5.65068101882935</v>
+        <v>5.65068197250366</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>7.75</v>
       </c>
       <c r="G822" t="n">
-        <v>5.5929479598999</v>
+        <v>5.59294843673706</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G827" t="n">
-        <v>5.62903213500977</v>
+        <v>5.62903118133545</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G828" t="n">
-        <v>5.62903213500977</v>
+        <v>5.62903118133545</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G829" t="n">
-        <v>5.7589316368103</v>
+        <v>5.75893211364746</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>5.62181377410889</v>
+        <v>5.6218147277832</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>5.48469686508179</v>
+        <v>5.48469734191895</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>5.54964780807495</v>
+        <v>5.54964733123779</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>5.53521394729614</v>
+        <v>5.5352144241333</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G838" t="n">
-        <v>5.51356363296509</v>
+        <v>5.51356410980225</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G843" t="n">
-        <v>5.29706287384033</v>
+        <v>5.29706239700317</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G845" t="n">
-        <v>5.51356363296509</v>
+        <v>5.51356410980225</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G846" t="n">
-        <v>5.5279974937439</v>
+        <v>5.52799701690674</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G847" t="n">
-        <v>5.55686473846436</v>
+        <v>5.5568642616272</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G849" t="n">
-        <v>5.34757995605469</v>
+        <v>5.34757947921753</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G852" t="n">
-        <v>5.12386131286621</v>
+        <v>5.12386178970337</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>5.15826654434204</v>
+        <v>5.1582670211792</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>5.112952709198</v>
+        <v>5.11295223236084</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G861" t="n">
-        <v>5.19602870941162</v>
+        <v>5.19602918624878</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G863" t="n">
-        <v>5.07519102096558</v>
+        <v>5.07519054412842</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>4.97701025009155</v>
+        <v>4.97700977325439</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G873" t="n">
-        <v>5.07519102096558</v>
+        <v>5.07519054412842</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G874" t="n">
-        <v>5.15826654434204</v>
+        <v>5.1582670211792</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G875" t="n">
-        <v>5.14316177368164</v>
+        <v>5.1431622505188</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G877" t="n">
-        <v>5.07519102096558</v>
+        <v>5.07519054412842</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G878" t="n">
-        <v>4.97701025009155</v>
+        <v>4.97700977325439</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>6.5</v>
       </c>
       <c r="G884" t="n">
-        <v>4.90903854370117</v>
+        <v>4.90903949737549</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G885" t="n">
-        <v>4.87127685546875</v>
+        <v>4.87127733230591</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>4.92414379119873</v>
+        <v>4.92414426803589</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>6.5</v>
       </c>
       <c r="G887" t="n">
-        <v>4.90903854370117</v>
+        <v>4.90903949737549</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G888" t="n">
-        <v>4.98456287384033</v>
+        <v>4.98456239700317</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>5.15826654434204</v>
+        <v>5.1582670211792</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G892" t="n">
-        <v>5.40749549865723</v>
+        <v>5.40749502182007</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G894" t="n">
-        <v>5.46791410446167</v>
+        <v>5.46791362762451</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G896" t="n">
-        <v>5.35462856292725</v>
+        <v>5.3546290397644</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G899" t="n">
-        <v>5.27910423278809</v>
+        <v>5.2791051864624</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>5.15826654434204</v>
+        <v>5.1582670211792</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G901" t="n">
-        <v>5.16582012176514</v>
+        <v>5.16581964492798</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G902" t="n">
-        <v>5.12050580978394</v>
+        <v>5.12050533294678</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G905" t="n">
-        <v>5.12805843353271</v>
+        <v>5.1280574798584</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>5.0072193145752</v>
+        <v>5.00722026824951</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G908" t="n">
-        <v>5.16582012176514</v>
+        <v>5.16581964492798</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G910" t="n">
-        <v>4.97701025009155</v>
+        <v>4.97700977325439</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G911" t="n">
-        <v>4.98456287384033</v>
+        <v>4.98456239700317</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G914" t="n">
-        <v>4.97701025009155</v>
+        <v>4.97700977325439</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G915" t="n">
-        <v>4.62204837799072</v>
+        <v>4.62204885482788</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G923" t="n">
-        <v>4.62204837799072</v>
+        <v>4.62204885482788</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>4.50121116638184</v>
+        <v>4.50121068954468</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G930" t="n">
-        <v>4.42568778991699</v>
+        <v>4.42568731307983</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G931" t="n">
-        <v>4.50121116638184</v>
+        <v>4.50121068954468</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G933" t="n">
-        <v>4.45589780807495</v>
+        <v>4.45589733123779</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G936" t="n">
-        <v>4.62204837799072</v>
+        <v>4.62204885482788</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>6.25</v>
       </c>
       <c r="G937" t="n">
-        <v>4.72023057937622</v>
+        <v>4.7202296257019</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>4.84106779098511</v>
+        <v>4.84106731414795</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G940" t="n">
-        <v>4.85617256164551</v>
+        <v>4.85617208480835</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G944" t="n">
-        <v>4.97701025009155</v>
+        <v>4.97700977325439</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G948" t="n">
-        <v>4.96945714950562</v>
+        <v>4.96945762634277</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>4.89393377304077</v>
+        <v>4.89393424987793</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>6.5</v>
       </c>
       <c r="G952" t="n">
-        <v>4.90903854370117</v>
+        <v>4.90903949737549</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>4.93924856185913</v>
+        <v>4.93924808502197</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G954" t="n">
-        <v>4.93924856185913</v>
+        <v>4.93924808502197</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>4.96945714950562</v>
+        <v>4.96945762634277</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>4.83351564407349</v>
+        <v>4.83351516723633</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G957" t="n">
-        <v>4.85617256164551</v>
+        <v>4.85617208480835</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>4.93924856185913</v>
+        <v>4.93924808502197</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G959" t="n">
-        <v>4.92414379119873</v>
+        <v>4.92414426803589</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G961" t="n">
-        <v>4.88638162612915</v>
+        <v>4.88638210296631</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G962" t="n">
-        <v>4.89393377304077</v>
+        <v>4.89393424987793</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G964" t="n">
-        <v>4.89393377304077</v>
+        <v>4.89393424987793</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G966" t="n">
-        <v>4.89393377304077</v>
+        <v>4.89393424987793</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G969" t="n">
-        <v>4.99211549758911</v>
+        <v>4.99211502075195</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.98456287384033</v>
+        <v>4.98456239700317</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G972" t="n">
-        <v>4.98456287384033</v>
+        <v>4.98456239700317</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G973" t="n">
-        <v>5.12050580978394</v>
+        <v>5.12050533294678</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>5.32441902160645</v>
+        <v>5.3244194984436</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G975" t="n">
-        <v>5.31686639785767</v>
+        <v>5.31686687469482</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G976" t="n">
-        <v>5.20358085632324</v>
+        <v>5.2035813331604</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G978" t="n">
-        <v>5.36218070983887</v>
+        <v>5.36218118667603</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G979" t="n">
-        <v>5.27910423278809</v>
+        <v>5.2791051864624</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G980" t="n">
-        <v>5.20358085632324</v>
+        <v>5.2035813331604</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G982" t="n">
-        <v>5.23379039764404</v>
+        <v>5.2337908744812</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G985" t="n">
-        <v>5.36218070983887</v>
+        <v>5.36218118667603</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G986" t="n">
-        <v>5.35462856292725</v>
+        <v>5.3546290397644</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G992" t="n">
-        <v>5.27910423278809</v>
+        <v>5.2791051864624</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G999" t="n">
-        <v>5.24134302139282</v>
+        <v>5.24134349822998</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1000" t="n">
-        <v>5.24134302139282</v>
+        <v>5.24134349822998</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1001" t="n">
-        <v>5.21113395690918</v>
+        <v>5.21113348007202</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1002" t="n">
-        <v>5.23379039764404</v>
+        <v>5.2337908744812</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1003" t="n">
-        <v>5.24134302139282</v>
+        <v>5.24134349822998</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1005" t="n">
-        <v>5.19602870941162</v>
+        <v>5.19602918624878</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1006" t="n">
-        <v>5.23379039764404</v>
+        <v>5.2337908744812</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1007" t="n">
-        <v>5.20358085632324</v>
+        <v>5.2035813331604</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1010" t="n">
-        <v>5.21113395690918</v>
+        <v>5.21113348007202</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1011" t="n">
-        <v>5.07519102096558</v>
+        <v>5.07519054412842</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1014" t="n">
-        <v>5.24134302139282</v>
+        <v>5.24134349822998</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1015" t="n">
-        <v>5.15071392059326</v>
+        <v>5.15071439743042</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.17337131500244</v>
+        <v>5.17337083816528</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.19602870941162</v>
+        <v>5.19602918624878</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1022" t="n">
-        <v>5.15071392059326</v>
+        <v>5.15071439743042</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.89393377304077</v>
+        <v>4.89393424987793</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.97701025009155</v>
+        <v>4.97700977325439</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.79575347900391</v>
+        <v>4.79575300216675</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.65981101989746</v>
+        <v>4.6598105430603</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.69757270812988</v>
+        <v>4.69757223129272</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.96945714950562</v>
+        <v>4.96945762634277</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.85617256164551</v>
+        <v>4.85617208480835</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.85617256164551</v>
+        <v>4.85617208480835</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.80330562591553</v>
+        <v>4.80330610275269</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.84106779098511</v>
+        <v>4.84106731414795</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>6.25</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.72023057937622</v>
+        <v>4.7202296257019</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.38037347793579</v>
+        <v>4.38037252426147</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>4.41058349609375</v>
+        <v>4.41058254241943</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.22932624816895</v>
+        <v>4.22932577133179</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.07072591781616</v>
+        <v>4.07072639465332</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.70066046714783</v>
+        <v>3.70066070556641</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.14178466796875</v>
+        <v>3.14178490638733</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.17199420928955</v>
+        <v>3.17199444770813</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.20220351219177</v>
+        <v>3.20220398902893</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.9831850528717</v>
+        <v>2.98318529129028</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.94542360305786</v>
+        <v>2.94542336463928</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.89255666732788</v>
+        <v>2.8925564289093</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>4</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.02094697952271</v>
+        <v>3.02094721794128</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.91899013519287</v>
+        <v>2.91898989677429</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.14178466796875</v>
+        <v>3.14178490638733</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.13423252105713</v>
+        <v>3.13423275947571</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.20220351219177</v>
+        <v>3.20220398902893</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.24374175071716</v>
+        <v>3.24374151229858</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.21730875968933</v>
+        <v>3.21730899810791</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.3305938243866</v>
+        <v>3.33059406280518</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.24751806259155</v>
+        <v>3.24751830101013</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.41367053985596</v>
+        <v>3.41367030143738</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>4.75</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.58737468719482</v>
+        <v>3.5873749256134</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.67045044898987</v>
+        <v>3.67045092582703</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.77618360519409</v>
+        <v>3.77618384361267</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1094" t="n">
-        <v>4.17645931243896</v>
+        <v>4.17645978927612</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1095" t="n">
-        <v>4.17645931243896</v>
+        <v>4.17645978927612</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.16135406494141</v>
+        <v>4.16135454177856</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1098" t="n">
-        <v>4.07827806472778</v>
+        <v>4.07827854156494</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1099" t="n">
-        <v>4.01030683517456</v>
+        <v>4.01030731201172</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.92723059654236</v>
+        <v>3.92723083496094</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>4.0631742477417</v>
+        <v>4.06317377090454</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.05562114715576</v>
+        <v>4.05562162399292</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1103" t="n">
-        <v>4.05562114715576</v>
+        <v>4.05562162399292</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1104" t="n">
-        <v>4.10093545913696</v>
+        <v>4.10093641281128</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1106" t="n">
-        <v>4.04051637649536</v>
+        <v>4.04051685333252</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.70066046714783</v>
+        <v>3.70066070556641</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.5949273109436</v>
+        <v>3.59492683410645</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.65534639358521</v>
+        <v>3.65534615516663</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.69310760498047</v>
+        <v>3.69310784339905</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>4.90500020980835</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.70443630218506</v>
+        <v>3.70443677902222</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.56471729278564</v>
+        <v>3.56471705436707</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.68933153152466</v>
+        <v>3.68933200836182</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.73086953163147</v>
+        <v>3.73086977005005</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.66289830207825</v>
+        <v>3.66289854049683</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>4.875</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.68177890777588</v>
+        <v>3.68177938461304</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.71954107284546</v>
+        <v>3.71954083442688</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>4.75</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.58737468719482</v>
+        <v>3.5873749256134</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.83660244941711</v>
+        <v>3.83660221099854</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1123" t="n">
-        <v>4.10093545913696</v>
+        <v>4.10093641281128</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1124" t="n">
-        <v>4.07827806472778</v>
+        <v>4.07827854156494</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.7724072933197</v>
+        <v>3.77240705490112</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.88946914672852</v>
+        <v>3.88946890830994</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.92723059654236</v>
+        <v>3.92723083496094</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.99520206451416</v>
+        <v>3.99520230293274</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.92723059654236</v>
+        <v>3.92723083496094</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.86681222915649</v>
+        <v>3.86681270599365</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.86681222915649</v>
+        <v>3.86681270599365</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.80639290809631</v>
+        <v>3.80639338493347</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.79884123802185</v>
+        <v>3.79884099960327</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.77618360519409</v>
+        <v>3.77618384361267</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.80639290809631</v>
+        <v>3.80639338493347</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.74597406387329</v>
+        <v>3.74597454071045</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>5</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.77618360519409</v>
+        <v>3.77618384361267</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.9045741558075</v>
+        <v>3.90457463264465</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.9045741558075</v>
+        <v>3.90457463264465</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.92723059654236</v>
+        <v>3.92723083496094</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.88946914672852</v>
+        <v>3.88946890830994</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.83660244941711</v>
+        <v>3.83660221099854</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.74975061416626</v>
+        <v>3.74975037574768</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.78373575210571</v>
+        <v>3.78373670578003</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.76863121986389</v>
+        <v>3.76863169670105</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.71576452255249</v>
+        <v>3.71576476097107</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.72331690788269</v>
+        <v>3.72331738471985</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.73842167854309</v>
+        <v>3.73842215538025</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.70066046714783</v>
+        <v>3.70066070556641</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.73842167854309</v>
+        <v>3.73842215538025</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.76863121986389</v>
+        <v>3.76863169670105</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.76485538482666</v>
+        <v>3.76485562324524</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.65534639358521</v>
+        <v>3.65534615516663</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.66289830207825</v>
+        <v>3.66289854049683</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.69310760498047</v>
+        <v>3.69310784339905</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.66289830207825</v>
+        <v>3.66289854049683</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.6175844669342</v>
+        <v>3.61758399009705</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.61003184318542</v>
+        <v>3.61003160476685</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.66667437553406</v>
+        <v>3.66667461395264</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.72331690788269</v>
+        <v>3.72331738471985</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.71954107284546</v>
+        <v>3.71954083442688</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.82149791717529</v>
+        <v>3.82149815559387</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.87436437606812</v>
+        <v>3.87436461448669</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.83660244941711</v>
+        <v>3.83660221099854</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>5</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.77618360519409</v>
+        <v>3.77618384361267</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.7724072933197</v>
+        <v>3.77240705490112</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.74597406387329</v>
+        <v>3.74597454071045</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.76863121986389</v>
+        <v>3.76863169670105</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.73842167854309</v>
+        <v>3.73842215538025</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.70066046714783</v>
+        <v>3.70066070556641</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.6251368522644</v>
+        <v>3.62513661384583</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.6175844669342</v>
+        <v>3.61758399009705</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.61003184318542</v>
+        <v>3.61003160476685</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.62136030197144</v>
+        <v>3.62136006355286</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.62136030197144</v>
+        <v>3.62136006355286</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.53450798988342</v>
+        <v>3.53450751304626</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.49674654006958</v>
+        <v>3.49674606323242</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.49674654006958</v>
+        <v>3.49674606323242</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.43632745742798</v>
+        <v>3.43632698059082</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.458984375</v>
+        <v>3.45898413658142</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.3608033657074</v>
+        <v>3.36080360412598</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.3154890537262</v>
+        <v>3.31548929214478</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.26262307167053</v>
+        <v>3.26262283325195</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.20220351219177</v>
+        <v>3.20220398902893</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.24374175071716</v>
+        <v>3.24374151229858</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.27772784233093</v>
+        <v>3.27772760391235</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.31171321868896</v>
+        <v>3.31171345710754</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.42499852180481</v>
+        <v>3.42499876022339</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.24751806259155</v>
+        <v>3.24751830101013</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.25507068634033</v>
+        <v>3.25507044792175</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.30793690681458</v>
+        <v>3.30793714523315</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.30038475990295</v>
+        <v>3.30038499832153</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.24751806259155</v>
+        <v>3.24751830101013</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.33437013626099</v>
+        <v>3.33437037467957</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.3154890537262</v>
+        <v>3.31548929214478</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.32304191589355</v>
+        <v>3.32304167747498</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.21730875968933</v>
+        <v>3.21730899810791</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.14178466796875</v>
+        <v>3.14178490638733</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.17199420928955</v>
+        <v>3.17199444770813</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.24751806259155</v>
+        <v>3.24751830101013</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.24751806259155</v>
+        <v>3.24751830101013</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.40234160423279</v>
+        <v>3.40234184265137</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.40611791610718</v>
+        <v>3.40611815452576</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.49674654006958</v>
+        <v>3.49674606323242</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.66289830207825</v>
+        <v>3.66289854049683</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.7724072933197</v>
+        <v>3.77240705490112</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.95744061470032</v>
+        <v>3.95744037628174</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.88946914672852</v>
+        <v>3.88946890830994</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.99520206451416</v>
+        <v>3.99520230293274</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.0480694770813</v>
+        <v>4.04806900024414</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.98009729385376</v>
+        <v>3.98009753227234</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.94233584403992</v>
+        <v>3.94233560562134</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.94233584403992</v>
+        <v>3.94233560562134</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.92723059654236</v>
+        <v>3.92723083496094</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.91212630271912</v>
+        <v>3.9121265411377</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.91212630271912</v>
+        <v>3.9121265411377</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.01030683517456</v>
+        <v>4.01030731201172</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.92723059654236</v>
+        <v>3.92723083496094</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.88946914672852</v>
+        <v>3.88946890830994</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.04051637649536</v>
+        <v>4.04051685333252</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.13114452362061</v>
+        <v>4.13114547729492</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.09338283538818</v>
+        <v>4.09338331222534</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.0858302116394</v>
+        <v>4.08583068847656</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1264" t="n">
-        <v>4.23687887191772</v>
+        <v>4.23687934875488</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.07827806472778</v>
+        <v>4.07827854156494</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1266" t="n">
-        <v>4.19911670684814</v>
+        <v>4.19911623001099</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1271" t="n">
-        <v>4.62204837799072</v>
+        <v>4.62204885482788</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.59183979034424</v>
+        <v>4.59183931350708</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.59939241409302</v>
+        <v>4.59939193725586</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>4.56163024902344</v>
+        <v>4.56162977218628</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.51631641387939</v>
+        <v>4.51631593704224</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.51631641387939</v>
+        <v>4.51631593704224</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.38037347793579</v>
+        <v>4.38037252426147</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.51631641387939</v>
+        <v>4.51631593704224</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1291" t="n">
-        <v>4.45589780807495</v>
+        <v>4.45589733123779</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1293" t="n">
-        <v>4.51631641387939</v>
+        <v>4.51631593704224</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1295" t="n">
-        <v>4.56163024902344</v>
+        <v>4.56162977218628</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.82596254348755</v>
+        <v>4.82596302032471</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>6.5</v>
       </c>
       <c r="G1300" t="n">
-        <v>4.90903854370117</v>
+        <v>4.90903949737549</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.97701025009155</v>
+        <v>4.97700977325439</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>6.5</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.90903854370117</v>
+        <v>4.90903949737549</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1303" t="n">
-        <v>4.81085777282715</v>
+        <v>4.81085824966431</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1305" t="n">
-        <v>4.80330562591553</v>
+        <v>4.80330610275269</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1306" t="n">
-        <v>4.79575347900391</v>
+        <v>4.79575300216675</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1307" t="n">
-        <v>4.68246793746948</v>
+        <v>4.68246841430664</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1308" t="n">
-        <v>4.66736268997192</v>
+        <v>4.66736316680908</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1310" t="n">
-        <v>4.62204837799072</v>
+        <v>4.62204885482788</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1311" t="n">
-        <v>4.7353343963623</v>
+        <v>4.73533391952515</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1315" t="n">
-        <v>4.69757270812988</v>
+        <v>4.69757223129272</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1316" t="n">
-        <v>4.7353343963623</v>
+        <v>4.73533391952515</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.89393377304077</v>
+        <v>4.89393424987793</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1319" t="n">
-        <v>4.98456287384033</v>
+        <v>4.98456239700317</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>5.07519102096558</v>
+        <v>5.07519054412842</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1322" t="n">
-        <v>5.24134302139282</v>
+        <v>5.24134349822998</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1325" t="n">
-        <v>5.39239072799683</v>
+        <v>5.39238977432251</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1327" t="n">
-        <v>5.27910423278809</v>
+        <v>5.2791051864624</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1328" t="n">
-        <v>5.32441902160645</v>
+        <v>5.3244194984436</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1331" t="n">
-        <v>5.50567626953125</v>
+        <v>5.50567579269409</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1332" t="n">
-        <v>5.48301935195923</v>
+        <v>5.48301887512207</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G1333" t="n">
-        <v>5.46036148071289</v>
+        <v>5.46036195755005</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1334" t="n">
-        <v>5.45280981063843</v>
+        <v>5.45280933380127</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1335" t="n">
-        <v>5.51322889328003</v>
+        <v>5.51322793960571</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1336" t="n">
-        <v>5.46791410446167</v>
+        <v>5.46791362762451</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1338" t="n">
-        <v>5.40749549865723</v>
+        <v>5.40749502182007</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1341" t="n">
-        <v>5.39239072799683</v>
+        <v>5.39238977432251</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1343" t="n">
-        <v>5.39239072799683</v>
+        <v>5.39238977432251</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1346" t="n">
-        <v>5.36218070983887</v>
+        <v>5.36218118667603</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1347" t="n">
-        <v>5.36218070983887</v>
+        <v>5.36218118667603</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1348" t="n">
-        <v>5.39239072799683</v>
+        <v>5.39238977432251</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1349" t="n">
-        <v>5.57364797592163</v>
+        <v>5.57364749908447</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1350" t="n">
-        <v>5.86063718795776</v>
+        <v>5.86063671112061</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1351" t="n">
-        <v>5.95126533508301</v>
+        <v>5.95126581192017</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1352" t="n">
-        <v>5.92105674743652</v>
+        <v>5.92105627059937</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G1355" t="n">
-        <v>5.75490427017212</v>
+        <v>5.75490379333496</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1356" t="n">
-        <v>5.81532287597656</v>
+        <v>5.81532335281372</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1357" t="n">
-        <v>5.81532287597656</v>
+        <v>5.81532335281372</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1358" t="n">
-        <v>5.81532287597656</v>
+        <v>5.81532335281372</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1364" t="n">
-        <v>6.2217698097229</v>
+        <v>6.22177028656006</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1367" t="n">
-        <v>6.17487192153931</v>
+        <v>6.17487239837646</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1369" t="n">
-        <v>6.17487192153931</v>
+        <v>6.17487239837646</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1371" t="n">
-        <v>6.17487192153931</v>
+        <v>6.17487239837646</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1372" t="n">
-        <v>6.70637989044189</v>
+        <v>6.70638036727905</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1375" t="n">
-        <v>7.70686531066895</v>
+        <v>7.70686626434326</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1376" t="n">
-        <v>7.55053949356079</v>
+        <v>7.55054044723511</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1377" t="n">
-        <v>7.58180522918701</v>
+        <v>7.58180570602417</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1387" t="n">
-        <v>8.12894439697266</v>
+        <v>8.12894535064697</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1394" t="n">
-        <v>7.67560052871704</v>
+        <v>7.67560148239136</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1396" t="n">
-        <v>6.98776626586914</v>
+        <v>6.98776721954346</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1398" t="n">
-        <v>7.36294937133789</v>
+        <v>7.36294841766357</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1402" t="n">
-        <v>7.44111251831055</v>
+        <v>7.44111204147339</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1408" t="n">
-        <v>6.95650148391724</v>
+        <v>6.95650196075439</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1409" t="n">
-        <v>6.56568670272827</v>
+        <v>6.56568717956543</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1410" t="n">
-        <v>6.89397096633911</v>
+        <v>6.89397144317627</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1412" t="n">
-        <v>7.11282777786255</v>
+        <v>7.11282730102539</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1426" t="n">
-        <v>8.51976013183594</v>
+        <v>8.51976108551025</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>8.51976013183594</v>
+        <v>8.51976108551025</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1428" t="n">
-        <v>8.44159698486328</v>
+        <v>8.4415979385376</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1431" t="n">
-        <v>8.44159698486328</v>
+        <v>8.4415979385376</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1433" t="n">
-        <v>8.12894439697266</v>
+        <v>8.12894535064697</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1442" t="n">
-        <v>8.12894439697266</v>
+        <v>8.12894535064697</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1444" t="n">
-        <v>8.12894439697266</v>
+        <v>8.12894535064697</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1445" t="n">
-        <v>8.12894439697266</v>
+        <v>8.12894535064697</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1449" t="n">
-        <v>8.12894439697266</v>
+        <v>8.12894535064697</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1452" t="n">
-        <v>8.12894439697266</v>
+        <v>8.12894535064697</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1458" t="n">
-        <v>8.12894439697266</v>
+        <v>8.12894535064697</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1463" t="n">
-        <v>7.75376319885254</v>
+        <v>7.75376415252686</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1464" t="n">
-        <v>7.67560052871704</v>
+        <v>7.67560148239136</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1465" t="n">
-        <v>8.71516895294189</v>
+        <v>8.71516799926758</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1466" t="n">
-        <v>8.51976013183594</v>
+        <v>8.51976108551025</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>9.06690120697021</v>
+        <v>9.0669002532959</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1468" t="n">
-        <v>8.83241271972656</v>
+        <v>8.83241176605225</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>12.25</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>10137</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>12.1999998092651</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>12.1999998092651</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>12.1999998092651</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>11.8500003814697</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>12</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>11078</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>12</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>11.6999998092651</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>9854</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>11.8000001907349</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>11.8999996185303</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>8206</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>11.4499998092651</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>11.75</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>11.4499998092651</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>11767</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>11.5500001907349</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>11.5500001907349</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>5601</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>11.4499998092651</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>11.4499998092651</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
